--- a/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
@@ -8,12 +8,18 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include ValueSet #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include ValueSet #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include ValueSet #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include ValueSet #5" r:id="rId9" sheetId="7"/>
+    <sheet name="Include ValueSet #6" r:id="rId10" sheetId="8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -384,7 +390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -401,33 +407,147 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>33</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>35</v>
       </c>
     </row>

--- a/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
@@ -8,18 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include ValueSet #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include ValueSet #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include ValueSet #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include ValueSet #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include ValueSet #4" r:id="rId8" sheetId="6"/>
-    <sheet name="Include ValueSet #5" r:id="rId9" sheetId="7"/>
-    <sheet name="Include ValueSet #6" r:id="rId10" sheetId="8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-05T09:00:00+00:00</t>
+    <t>2026-09-10T09:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,25 +102,7 @@
     <t>ValueSet URL</t>
   </si>
   <si>
-    <t>http://ehealth.sundhed.dk/vs/ehealth-treatment-area-xb-1</t>
-  </si>
-  <si>
-    <t>http://ehealth.sundhed.dk/vs/ehealth-treatment-area-xb-2</t>
-  </si>
-  <si>
-    <t>http://ehealth.sundhed.dk/vs/ehealth-treatment-area-xb-3</t>
-  </si>
-  <si>
-    <t>http://ehealth.sundhed.dk/vs/ehealth-treatment-area-xb-4</t>
-  </si>
-  <si>
-    <t>http://ehealth.sundhed.dk/vs/ehealth-treatment-area-xb-5</t>
-  </si>
-  <si>
-    <t>http://ehealth.sundhed.dk/vs/ehealth-treatment-area-xb-6</t>
-  </si>
-  <si>
-    <t>http://ehealth.sundhed.dk/vs/ehealth-treatment-area-xb-7</t>
+    <t>http://ehealth.sundhed.dk/vs/ehealth-treatment-area-all-conditions</t>
   </si>
 </sst>
 </file>
@@ -410,148 +386,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
+++ b/fhir/ValueSet-ehealth-treatment-areas-xb.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
